--- a/vse-loti/340778290/spec-340778290.xlsx
+++ b/vse-loti/340778290/spec-340778290.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -551,13 +554,13 @@
         <v>621.6950000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>65115196.72</v>
+        <v>79440540</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>104738.08</v>
+        <v>127780.49</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>127780.46</v>
+        <v>127780.49</v>
       </c>
     </row>
     <row r="3">
@@ -570,7 +573,7 @@
         <v>621.6950000000001</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>65115196.72</v>
+        <v>79440540</v>
       </c>
     </row>
     <row r="4">
@@ -580,21 +583,18 @@
         </is>
       </c>
       <c r="G4" s="8" t="n">
-        <v>65115196.72</v>
+        <v>79440540</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>НМЦК с НДС 22%:</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>79440540</v>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>НДС не облагается, из документа: "лиона девятьсот семьдесят две тысячи двадцать семь) рублей 00 копеек, НДС не облагается." — Dokumentatsiya.txt. Цена за тонну в обеих колонках одинаковая.</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Источник: Обоснование НМЦД.doc</t>
         </is>

--- a/vse-loti/340778290/spec-340778290.xlsx
+++ b/vse-loti/340778290/spec-340778290.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -513,17 +514,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -554,13 +560,16 @@
         <v>621.6950000000001</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>127780.49</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>79440540</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>127780.49</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>127780.49</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>79440540</v>
       </c>
     </row>
     <row r="3">
@@ -573,6 +582,15 @@
         <v>621.6950000000001</v>
       </c>
       <c r="G3" s="8" t="n">
+        <v>127780.57</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>79440540</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>127780.57</v>
+      </c>
+      <c r="J3" s="8" t="n">
         <v>79440540</v>
       </c>
     </row>
@@ -582,7 +600,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="H4" s="8" t="n">
         <v>79440540</v>
       </c>
     </row>
